--- a/reports/Debug-purgatory-20260111/purgatory_Report_20260111.xlsx
+++ b/reports/Debug-purgatory-20260111/purgatory_Report_20260111.xlsx
@@ -1249,7 +1249,7 @@
         <v>6383</v>
       </c>
       <c r="I9" s="4">
-        <v>12149</v>
+        <v>12148</v>
       </c>
       <c r="J9" s="4">
         <v>13848</v>
@@ -1258,7 +1258,7 @@
         <v>14891</v>
       </c>
       <c r="L9" s="4">
-        <v>34074</v>
+        <v>34072</v>
       </c>
       <c r="M9" s="4">
         <v>46638</v>
@@ -1337,7 +1337,7 @@
         <v>19349</v>
       </c>
       <c r="I11" s="4">
-        <v>29593</v>
+        <v>29592</v>
       </c>
       <c r="J11" s="4">
         <v>37268</v>
@@ -1346,7 +1346,7 @@
         <v>40667</v>
       </c>
       <c r="L11" s="4">
-        <v>83616</v>
+        <v>83614</v>
       </c>
       <c r="M11" s="4">
         <v>118801</v>
@@ -1541,7 +1541,7 @@
         <v>28</v>
       </c>
       <c r="B18" s="4">
-        <v>4452.176388888889</v>
+        <v>4452.17638888889</v>
       </c>
       <c r="C18" s="4">
         <v>5553.77</v>
@@ -1673,7 +1673,7 @@
         <v>31</v>
       </c>
       <c r="B21" s="4">
-        <v>1731.377222222223</v>
+        <v>1731.377222222222</v>
       </c>
       <c r="C21" s="4">
         <v>1347.67</v>
@@ -1703,7 +1703,7 @@
         <v>23918.06</v>
       </c>
       <c r="L21" s="4">
-        <v>130467.0661527778</v>
+        <v>130467.0661527777</v>
       </c>
       <c r="M21" s="4">
         <v>147872.84</v>
@@ -1826,7 +1826,7 @@
         <v>5953.26</v>
       </c>
       <c r="I24" s="4">
-        <v>21720.1598888889</v>
+        <v>21720.15988888889</v>
       </c>
       <c r="J24" s="4">
         <v>8369.799999999999</v>
@@ -1937,7 +1937,7 @@
         <v>37</v>
       </c>
       <c r="B27" s="4">
-        <v>848.2396194444444</v>
+        <v>848.2396194444443</v>
       </c>
       <c r="C27" s="4">
         <v>808.2</v>
@@ -1958,7 +1958,7 @@
         <v>5422.13</v>
       </c>
       <c r="I27" s="4">
-        <v>7780.815286111111</v>
+        <v>7780.815286111112</v>
       </c>
       <c r="J27" s="4">
         <v>8452.200000000001</v>
@@ -1967,7 +1967,7 @@
         <v>8425.41</v>
       </c>
       <c r="L27" s="4">
-        <v>45321.41861944445</v>
+        <v>45321.41861944446</v>
       </c>
       <c r="M27" s="4">
         <v>45555.7</v>
@@ -2210,7 +2210,7 @@
         <v>915.73</v>
       </c>
       <c r="E33" s="4">
-        <v>9001.284058333333</v>
+        <v>9001.284058333335</v>
       </c>
       <c r="F33" s="4">
         <v>9177.690000000001</v>
@@ -2222,7 +2222,7 @@
         <v>6189.67</v>
       </c>
       <c r="I33" s="4">
-        <v>15132.82309166667</v>
+        <v>15132.82309166666</v>
       </c>
       <c r="J33" s="4">
         <v>13443.45</v>
@@ -2231,7 +2231,7 @@
         <v>9933.059999999999</v>
       </c>
       <c r="L33" s="4">
-        <v>89017.42395000003</v>
+        <v>89017.42394999997</v>
       </c>
       <c r="M33" s="4">
         <v>95139.36</v>
@@ -2333,7 +2333,7 @@
         <v>46</v>
       </c>
       <c r="B36" s="4">
-        <v>4390.088511111112</v>
+        <v>4390.088511111111</v>
       </c>
       <c r="C36" s="4">
         <v>4950.8</v>
@@ -2354,7 +2354,7 @@
         <v>29999.4</v>
       </c>
       <c r="I36" s="4">
-        <v>44116.50561666668</v>
+        <v>44116.50561666667</v>
       </c>
       <c r="J36" s="4">
         <v>50141.18</v>
@@ -2363,7 +2363,7 @@
         <v>49854.76</v>
       </c>
       <c r="L36" s="4">
-        <v>187293.9505138889</v>
+        <v>187293.9505138887</v>
       </c>
       <c r="M36" s="4">
         <v>240169.39</v>
@@ -2424,7 +2424,7 @@
         <v>41131.73</v>
       </c>
       <c r="C38" s="4">
-        <v>140480.5</v>
+        <v>132675.3</v>
       </c>
       <c r="D38" s="4">
         <v>55151.85</v>
@@ -2433,7 +2433,7 @@
         <v>473501.88</v>
       </c>
       <c r="F38" s="4">
-        <v>1233730.74</v>
+        <v>1130935.94</v>
       </c>
       <c r="G38" s="4">
         <v>331031.4</v>
@@ -2445,7 +2445,7 @@
         <v>1183600.1</v>
       </c>
       <c r="J38" s="4">
-        <v>2428900.14</v>
+        <v>2326105.34</v>
       </c>
       <c r="K38" s="4">
         <v>682151.9</v>
@@ -2454,7 +2454,7 @@
         <v>2885884.77</v>
       </c>
       <c r="M38" s="4">
-        <v>6987049.79</v>
+        <v>6791034.99</v>
       </c>
       <c r="N38" s="4">
         <v>1838979.92</v>
@@ -2465,7 +2465,7 @@
         <v>49</v>
       </c>
       <c r="B39" s="4">
-        <v>3759.285083333332</v>
+        <v>3759.285083333333</v>
       </c>
       <c r="C39" s="4">
         <v>1204.15</v>
@@ -2486,7 +2486,7 @@
         <v>8242.940000000001</v>
       </c>
       <c r="I39" s="4">
-        <v>48613.98018333341</v>
+        <v>48613.98018333338</v>
       </c>
       <c r="J39" s="4">
         <v>13439.63</v>
@@ -2495,7 +2495,7 @@
         <v>14705.7</v>
       </c>
       <c r="L39" s="4">
-        <v>202788.7735888886</v>
+        <v>202788.7735888888</v>
       </c>
       <c r="M39" s="4">
         <v>55575.33</v>
@@ -2509,19 +2509,19 @@
         <v>50</v>
       </c>
       <c r="B40" s="5">
-        <v>9.139623067965612</v>
+        <v>9.139623067965614</v>
       </c>
       <c r="C40" s="5">
-        <v>0.8571652293378798</v>
+        <v>0.907591691897437</v>
       </c>
       <c r="D40" s="5">
         <v>1.939717344023818</v>
       </c>
       <c r="E40" s="5">
-        <v>6.086324967589239</v>
+        <v>6.08632496758924</v>
       </c>
       <c r="F40" s="5">
-        <v>0.6114000207208908</v>
+        <v>0.6669723485841295</v>
       </c>
       <c r="G40" s="5">
         <v>2.49007798051786</v>
@@ -2530,19 +2530,19 @@
         <v>2.49007798051786</v>
       </c>
       <c r="I40" s="5">
-        <v>4.107297742145628</v>
+        <v>4.107297742145626</v>
       </c>
       <c r="J40" s="5">
-        <v>0.5533216363518344</v>
+        <v>0.5777739197314254</v>
       </c>
       <c r="K40" s="5">
         <v>2.155780845879048</v>
       </c>
       <c r="L40" s="5">
-        <v>7.026918596922657</v>
+        <v>7.026918596922662</v>
       </c>
       <c r="M40" s="5">
-        <v>0.7954048084721034</v>
+        <v>0.8183631814861256</v>
       </c>
       <c r="N40" s="5">
         <v>3.933211516523791</v>
@@ -2729,7 +2729,7 @@
         <v>55</v>
       </c>
       <c r="B45" s="4">
-        <v>4998.579055555556</v>
+        <v>4998.579055555555</v>
       </c>
       <c r="C45" s="4">
         <v>3096.22</v>
@@ -2759,7 +2759,7 @@
         <v>86054.48</v>
       </c>
       <c r="L45" s="4">
-        <v>237061.7509916663</v>
+        <v>237061.7509916665</v>
       </c>
       <c r="M45" s="4">
         <v>267111.95</v>
@@ -2773,7 +2773,7 @@
         <v>56</v>
       </c>
       <c r="B46" s="5">
-        <v>21.04424739558373</v>
+        <v>21.04424739558372</v>
       </c>
       <c r="C46" s="5">
         <v>26.67085881643552</v>
@@ -2803,7 +2803,7 @@
         <v>22.43948785454566</v>
       </c>
       <c r="L46" s="5">
-        <v>28.22218298766688</v>
+        <v>28.2221829876669</v>
       </c>
       <c r="M46" s="5">
         <v>22.34668758265437</v>
@@ -3023,7 +3023,7 @@
         <v>16814.8</v>
       </c>
       <c r="L51" s="4">
-        <v>7000.417127777779</v>
+        <v>7000.417127777778</v>
       </c>
       <c r="M51" s="4">
         <v>85617.52</v>
@@ -3067,7 +3067,7 @@
         <v>5.309915993698257</v>
       </c>
       <c r="L52" s="5">
-        <v>0.7212593897254005</v>
+        <v>0.7212593897254004</v>
       </c>
       <c r="M52" s="5">
         <v>7.213315684546384</v>
@@ -3348,7 +3348,7 @@
         <v>7824.55</v>
       </c>
       <c r="C59" s="4">
-        <v>11930.88</v>
+        <v>9407.040000000001</v>
       </c>
       <c r="D59" s="4">
         <v>5088.05</v>
@@ -3357,7 +3357,7 @@
         <v>73395</v>
       </c>
       <c r="F59" s="4">
-        <v>91907.63</v>
+        <v>72465.73</v>
       </c>
       <c r="G59" s="4">
         <v>65571.25999999999</v>
@@ -3369,7 +3369,7 @@
         <v>130481.63</v>
       </c>
       <c r="J59" s="4">
-        <v>186041.73</v>
+        <v>146686.89</v>
       </c>
       <c r="K59" s="4">
         <v>131902.85</v>
@@ -3378,7 +3378,7 @@
         <v>385494.55</v>
       </c>
       <c r="M59" s="4">
-        <v>593054.03</v>
+        <v>467600.93</v>
       </c>
       <c r="N59" s="4">
         <v>552576.41</v>
@@ -3436,7 +3436,7 @@
         <v>0.6995929478372558</v>
       </c>
       <c r="C61" s="5">
-        <v>3.197584754854629</v>
+        <v>4.055473347620505</v>
       </c>
       <c r="D61" s="5">
         <v>26.85508200587651</v>
@@ -3445,7 +3445,7 @@
         <v>0.5457388105456775</v>
       </c>
       <c r="F61" s="5">
-        <v>4.107167163379144</v>
+        <v>5.20908296928769</v>
       </c>
       <c r="G61" s="5">
         <v>16.21468002902492</v>
@@ -3457,7 +3457,7 @@
         <v>0.4404336457170255</v>
       </c>
       <c r="J61" s="5">
-        <v>3.347808042851461</v>
+        <v>4.245996353184664</v>
       </c>
       <c r="K61" s="5">
         <v>12.02395550968004</v>
@@ -3466,7 +3466,7 @@
         <v>2.421900341320576</v>
       </c>
       <c r="M61" s="5">
-        <v>4.750916202356807</v>
+        <v>6.025544046715219</v>
       </c>
       <c r="N61" s="5">
         <v>10.9556015972524</v>
@@ -3480,7 +3480,7 @@
         <v>620.1900000000001</v>
       </c>
       <c r="C62" s="4">
-        <v>2776.03</v>
+        <v>2010.49</v>
       </c>
       <c r="D62" s="4">
         <v>3284.86</v>
@@ -3489,7 +3489,7 @@
         <v>10648.32</v>
       </c>
       <c r="F62" s="4">
-        <v>25975.73</v>
+        <v>20078.47</v>
       </c>
       <c r="G62" s="4">
         <v>12177.7</v>
@@ -3501,7 +3501,7 @@
         <v>32585.4</v>
       </c>
       <c r="J62" s="4">
-        <v>53734.14</v>
+        <v>41796.66</v>
       </c>
       <c r="K62" s="4">
         <v>35784.01</v>
@@ -3510,7 +3510,7 @@
         <v>138639.75</v>
       </c>
       <c r="M62" s="4">
-        <v>188438.72</v>
+        <v>149255.7</v>
       </c>
       <c r="N62" s="4">
         <v>188782.34</v>
@@ -3568,7 +3568,7 @@
         <v>25.72329984897101</v>
       </c>
       <c r="C64" s="5">
-        <v>23.40608711000962</v>
+        <v>32.31848952245473</v>
       </c>
       <c r="D64" s="5">
         <v>15.51816515772362</v>
@@ -3577,7 +3577,7 @@
         <v>13.02333764074208</v>
       </c>
       <c r="F64" s="5">
-        <v>16.49539781942606</v>
+        <v>21.3402714449856</v>
       </c>
       <c r="G64" s="5">
         <v>32.96607733808519</v>
@@ -3589,7 +3589,7 @@
         <v>6.351044741919182</v>
       </c>
       <c r="J64" s="5">
-        <v>14.09963944710011</v>
+        <v>18.12661585877914</v>
       </c>
       <c r="K64" s="5">
         <v>18.3984690368687</v>
@@ -3598,7 +3598,7 @@
         <v>12.41789632242316</v>
       </c>
       <c r="M64" s="5">
-        <v>17.41833100967784</v>
+        <v>21.99103953818849</v>
       </c>
       <c r="N64" s="5">
         <v>21.23360691471458</v>
@@ -3612,7 +3612,7 @@
         <v>3114.94</v>
       </c>
       <c r="C65" s="4">
-        <v>4282.88</v>
+        <v>3365.12</v>
       </c>
       <c r="D65" s="4">
         <v>1469.74</v>
@@ -3621,7 +3621,7 @@
         <v>29265.07</v>
       </c>
       <c r="F65" s="4">
-        <v>32992.4</v>
+        <v>25922.66</v>
       </c>
       <c r="G65" s="4">
         <v>18675.71</v>
@@ -3633,7 +3633,7 @@
         <v>58442.26</v>
       </c>
       <c r="J65" s="4">
-        <v>66784.07000000001</v>
+        <v>52473.31</v>
       </c>
       <c r="K65" s="4">
         <v>47592.88</v>
@@ -3642,7 +3642,7 @@
         <v>153763.22</v>
       </c>
       <c r="M65" s="4">
-        <v>212890.42</v>
+        <v>167271.6</v>
       </c>
       <c r="N65" s="4">
         <v>150658.86</v>
@@ -3700,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="C67" s="5">
-        <v>3.239642483562462</v>
+        <v>4.123181342715862</v>
       </c>
       <c r="D67" s="5">
         <v>0</v>
@@ -3709,7 +3709,7 @@
         <v>0</v>
       </c>
       <c r="F67" s="5">
-        <v>3.341678689637614</v>
+        <v>4.253035760990578</v>
       </c>
       <c r="G67" s="5">
         <v>0</v>
@@ -3721,7 +3721,7 @@
         <v>0</v>
       </c>
       <c r="J67" s="5">
-        <v>3.267994897585606</v>
+        <v>4.159257344352777</v>
       </c>
       <c r="K67" s="5">
         <v>0</v>
@@ -3730,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="M67" s="5">
-        <v>4.090132378901784</v>
+        <v>5.205605733429943</v>
       </c>
       <c r="N67" s="5">
         <v>0</v>
@@ -3876,7 +3876,7 @@
         <v>4065.77</v>
       </c>
       <c r="C71" s="4">
-        <v>4738.94</v>
+        <v>4537.84</v>
       </c>
       <c r="D71" s="4">
         <v>4244.45</v>
@@ -3885,7 +3885,7 @@
         <v>34315.88</v>
       </c>
       <c r="F71" s="4">
-        <v>36505.66</v>
+        <v>34956.44</v>
       </c>
       <c r="G71" s="4">
         <v>24527.62</v>
@@ -3897,7 +3897,7 @@
         <v>63148.13</v>
       </c>
       <c r="J71" s="4">
-        <v>73895.7</v>
+        <v>70759.64</v>
       </c>
       <c r="K71" s="4">
         <v>59636.86</v>
@@ -3906,7 +3906,7 @@
         <v>184007.96</v>
       </c>
       <c r="M71" s="4">
-        <v>235560.77</v>
+        <v>225564.15</v>
       </c>
       <c r="N71" s="4">
         <v>193993.93</v>
@@ -3938,7 +3938,7 @@
         <v>6365.54</v>
       </c>
       <c r="I72" s="4">
-        <v>7962.091294444448</v>
+        <v>7962.091294444447</v>
       </c>
       <c r="J72" s="4">
         <v>10209.98</v>
@@ -3964,7 +3964,7 @@
         <v>8.904455845865469</v>
       </c>
       <c r="C73" s="5">
-        <v>20.47926329516728</v>
+        <v>21.38682721294713</v>
       </c>
       <c r="D73" s="5">
         <v>23.68693234694719</v>
@@ -3973,7 +3973,7 @@
         <v>12.87950721033204</v>
       </c>
       <c r="F73" s="5">
-        <v>17.50616205815755</v>
+        <v>18.28201041067111</v>
       </c>
       <c r="G73" s="5">
         <v>25.95253840364454</v>
@@ -3985,7 +3985,7 @@
         <v>12.60859394323228</v>
       </c>
       <c r="J73" s="5">
-        <v>13.81674441137982</v>
+        <v>14.4291011090503</v>
       </c>
       <c r="K73" s="5">
         <v>17.91018172318261</v>
@@ -3994,7 +3994,7 @@
         <v>17.97275304014023</v>
       </c>
       <c r="M73" s="5">
-        <v>18.45227454469605</v>
+        <v>19.2700480107322</v>
       </c>
       <c r="N73" s="5">
         <v>21.78311455415126</v>
@@ -4008,7 +4008,7 @@
         <v>2909.12</v>
       </c>
       <c r="C74" s="4">
-        <v>6891.44</v>
+        <v>6471.78</v>
       </c>
       <c r="D74" s="4">
         <v>5761.44</v>
@@ -4017,7 +4017,7 @@
         <v>29034.69</v>
       </c>
       <c r="F74" s="4">
-        <v>53087.17</v>
+        <v>49854.33</v>
       </c>
       <c r="G74" s="4">
         <v>47408.21</v>
@@ -4029,7 +4029,7 @@
         <v>50951.21</v>
       </c>
       <c r="J74" s="4">
-        <v>107460.37</v>
+        <v>100916.35</v>
       </c>
       <c r="K74" s="4">
         <v>105866.12</v>
@@ -4038,7 +4038,7 @@
         <v>66889.98</v>
       </c>
       <c r="M74" s="4">
-        <v>274475.48</v>
+        <v>257760.8</v>
       </c>
       <c r="N74" s="4">
         <v>231253.79</v>
@@ -4070,7 +4070,7 @@
         <v>18995.44</v>
       </c>
       <c r="I75" s="4">
-        <v>15472.81185555556</v>
+        <v>15472.81185555555</v>
       </c>
       <c r="J75" s="4">
         <v>28473.89</v>
@@ -4079,7 +4079,7 @@
         <v>31531</v>
       </c>
       <c r="L75" s="4">
-        <v>34614.46098333331</v>
+        <v>34614.46098333329</v>
       </c>
       <c r="M75" s="4">
         <v>72749.42999999999</v>
@@ -4096,7 +4096,7 @@
         <v>43.61052196769698</v>
       </c>
       <c r="C76" s="5">
-        <v>43.23073261901722</v>
+        <v>46.03401228101079</v>
       </c>
       <c r="D76" s="5">
         <v>39.33825571384931</v>
@@ -4105,7 +4105,7 @@
         <v>29.63307217829584</v>
       </c>
       <c r="F76" s="5">
-        <v>32.99077724429462</v>
+        <v>35.13008799837446</v>
       </c>
       <c r="G76" s="5">
         <v>40.06782791419461</v>
@@ -4114,19 +4114,19 @@
         <v>40.06782791419461</v>
       </c>
       <c r="I76" s="5">
-        <v>30.36789873205279</v>
+        <v>30.36789873205278</v>
       </c>
       <c r="J76" s="5">
-        <v>26.49710772445693</v>
+        <v>28.21533874342463</v>
       </c>
       <c r="K76" s="5">
         <v>29.78384397199029</v>
       </c>
       <c r="L76" s="5">
-        <v>51.74835002691481</v>
+        <v>51.74835002691479</v>
       </c>
       <c r="M76" s="5">
-        <v>26.50489216741692</v>
+        <v>28.22362050397112</v>
       </c>
       <c r="N76" s="5">
         <v>32.06001510288761</v>
@@ -4272,7 +4272,7 @@
         <v>637.13</v>
       </c>
       <c r="C80" s="4">
-        <v>1012.32</v>
+        <v>938.34</v>
       </c>
       <c r="D80" s="4">
         <v>796.22</v>
@@ -4281,7 +4281,7 @@
         <v>5046.02</v>
       </c>
       <c r="F80" s="4">
-        <v>7798.2</v>
+        <v>7228.44</v>
       </c>
       <c r="G80" s="4">
         <v>5508.59</v>
@@ -4293,7 +4293,7 @@
         <v>11670.15</v>
       </c>
       <c r="J80" s="4">
-        <v>15785.37</v>
+        <v>14631.95</v>
       </c>
       <c r="K80" s="4">
         <v>13696.17</v>
@@ -4302,7 +4302,7 @@
         <v>29004.11</v>
       </c>
       <c r="M80" s="4">
-        <v>44370.34</v>
+        <v>41128.3</v>
       </c>
       <c r="N80" s="4">
         <v>27549.62</v>
@@ -4343,7 +4343,7 @@
         <v>2155.29</v>
       </c>
       <c r="L81" s="4">
-        <v>6776.063422222223</v>
+        <v>6776.063422222221</v>
       </c>
       <c r="M81" s="4">
         <v>10615.76</v>
@@ -4360,7 +4360,7 @@
         <v>21.25417104829469</v>
       </c>
       <c r="C82" s="5">
-        <v>18.15927769875138</v>
+        <v>19.59097981541872</v>
       </c>
       <c r="D82" s="5">
         <v>16.06967923438246</v>
@@ -4369,7 +4369,7 @@
         <v>36.96134313115419</v>
       </c>
       <c r="F82" s="5">
-        <v>15.74222256418148</v>
+        <v>16.98305581840619</v>
       </c>
       <c r="G82" s="5">
         <v>24.98897176954538</v>
@@ -4381,16 +4381,16 @@
         <v>26.4771647703281</v>
       </c>
       <c r="J82" s="5">
-        <v>13.87696328942559</v>
+        <v>14.97086854452072</v>
       </c>
       <c r="K82" s="5">
         <v>15.73644310781773</v>
       </c>
       <c r="L82" s="5">
-        <v>23.36242491916568</v>
+        <v>23.36242491916567</v>
       </c>
       <c r="M82" s="5">
-        <v>23.92535193554974</v>
+        <v>25.81132699382177</v>
       </c>
       <c r="N82" s="5">
         <v>20.88355483669103</v>
@@ -4445,7 +4445,7 @@
         <v>94</v>
       </c>
       <c r="B84" s="4">
-        <v>742.4394444444445</v>
+        <v>742.4394444444443</v>
       </c>
       <c r="C84" s="4">
         <v>553.9</v>
@@ -4466,7 +4466,7 @@
         <v>4847.04</v>
       </c>
       <c r="I84" s="4">
-        <v>9013.161488888889</v>
+        <v>9013.161488888887</v>
       </c>
       <c r="J84" s="4">
         <v>6028.9</v>
@@ -4475,7 +4475,7 @@
         <v>7489.9</v>
       </c>
       <c r="L84" s="4">
-        <v>44071.60887777777</v>
+        <v>44071.60887777778</v>
       </c>
       <c r="M84" s="4">
         <v>30172.72</v>
@@ -4489,7 +4489,7 @@
         <v>95</v>
       </c>
       <c r="B85" s="5">
-        <v>102.4308717260071</v>
+        <v>102.430871726007</v>
       </c>
       <c r="C85" s="5">
         <v>50.80952162546438</v>
@@ -4536,7 +4536,7 @@
         <v>3549.83</v>
       </c>
       <c r="C86" s="4">
-        <v>4419.48</v>
+        <v>3986.78</v>
       </c>
       <c r="D86" s="4">
         <v>3728.74</v>
@@ -4545,7 +4545,7 @@
         <v>32562.83</v>
       </c>
       <c r="F86" s="4">
-        <v>34044.82</v>
+        <v>30711.58</v>
       </c>
       <c r="G86" s="4">
         <v>27582.45</v>
@@ -4557,7 +4557,7 @@
         <v>59519</v>
       </c>
       <c r="J86" s="4">
-        <v>68914.39999999999</v>
+        <v>62167.14</v>
       </c>
       <c r="K86" s="4">
         <v>59327.7</v>
@@ -4566,7 +4566,7 @@
         <v>145472.95</v>
       </c>
       <c r="M86" s="4">
-        <v>194410.75</v>
+        <v>174040.59</v>
       </c>
       <c r="N86" s="4">
         <v>126551.07</v>
@@ -4607,7 +4607,7 @@
         <v>22605.25</v>
       </c>
       <c r="L87" s="4">
-        <v>63494.2092444445</v>
+        <v>63494.20924444452</v>
       </c>
       <c r="M87" s="4">
         <v>58800.36</v>
@@ -4624,7 +4624,7 @@
         <v>47.19030613985583</v>
       </c>
       <c r="C88" s="5">
-        <v>29.31973897381593</v>
+        <v>32.50191884177205</v>
       </c>
       <c r="D88" s="5">
         <v>43.45194355197734</v>
@@ -4633,7 +4633,7 @@
         <v>36.83303027818324</v>
       </c>
       <c r="F88" s="5">
-        <v>28.0304316486326</v>
+        <v>31.07267682092553</v>
       </c>
       <c r="G88" s="5">
         <v>47.5300417475605</v>
@@ -4645,16 +4645,16 @@
         <v>33.07190654338205</v>
       </c>
       <c r="J88" s="5">
-        <v>22.54076071183962</v>
+        <v>24.98720385078033</v>
       </c>
       <c r="K88" s="5">
         <v>38.10235353806064</v>
       </c>
       <c r="L88" s="5">
-        <v>43.64674617820323</v>
+        <v>43.64674617820324</v>
       </c>
       <c r="M88" s="5">
-        <v>30.24542624314756</v>
+        <v>33.78542901974764</v>
       </c>
       <c r="N88" s="5">
         <v>46.89311595705986</v>
@@ -4668,7 +4668,7 @@
         <v>8624.950000000001</v>
       </c>
       <c r="C89" s="4">
-        <v>13192.04</v>
+        <v>12594.14</v>
       </c>
       <c r="D89" s="4">
         <v>9689.84</v>
@@ -4677,7 +4677,7 @@
         <v>81640.28</v>
       </c>
       <c r="F89" s="4">
-        <v>101622.87</v>
+        <v>97017.09</v>
       </c>
       <c r="G89" s="4">
         <v>84142.10000000001</v>
@@ -4689,7 +4689,7 @@
         <v>151631.01</v>
       </c>
       <c r="J89" s="4">
-        <v>205707.55</v>
+        <v>196384.33</v>
       </c>
       <c r="K89" s="4">
         <v>169223.58</v>
@@ -4698,7 +4698,7 @@
         <v>473607.85</v>
       </c>
       <c r="M89" s="4">
-        <v>719487.72</v>
+        <v>689767.9399999999</v>
       </c>
       <c r="N89" s="4">
         <v>594588.13</v>
@@ -4709,7 +4709,7 @@
         <v>100</v>
       </c>
       <c r="B90" s="4">
-        <v>2664.769005555556</v>
+        <v>2664.769005555555</v>
       </c>
       <c r="C90" s="4">
         <v>2925.1</v>
@@ -4730,7 +4730,7 @@
         <v>17186.04</v>
       </c>
       <c r="I90" s="4">
-        <v>26945.34110833333</v>
+        <v>26945.34110833334</v>
       </c>
       <c r="J90" s="4">
         <v>35429.3</v>
@@ -4739,7 +4739,7 @@
         <v>31024.94</v>
       </c>
       <c r="L90" s="4">
-        <v>114317.8991583332</v>
+        <v>114317.8991583331</v>
       </c>
       <c r="M90" s="4">
         <v>141910.72</v>
@@ -4753,10 +4753,10 @@
         <v>101</v>
       </c>
       <c r="B91" s="5">
-        <v>30.89605163572607</v>
+        <v>30.89605163572606</v>
       </c>
       <c r="C91" s="5">
-        <v>22.17321960818797</v>
+        <v>23.22588124318136</v>
       </c>
       <c r="D91" s="5">
         <v>23.91670037895362</v>
@@ -4765,7 +4765,7 @@
         <v>19.13743405828594</v>
       </c>
       <c r="F91" s="5">
-        <v>20.05188399028683</v>
+        <v>21.00382520234322</v>
       </c>
       <c r="G91" s="5">
         <v>20.42501910458617</v>
@@ -4777,16 +4777,16 @@
         <v>17.77033675917171</v>
       </c>
       <c r="J91" s="5">
-        <v>17.22314032712946</v>
+        <v>18.04079785795537</v>
       </c>
       <c r="K91" s="5">
         <v>18.33369793973157</v>
       </c>
       <c r="L91" s="5">
-        <v>24.13766983767968</v>
+        <v>24.13766983767966</v>
       </c>
       <c r="M91" s="5">
-        <v>19.7238557455852</v>
+        <v>20.57369033417239</v>
       </c>
       <c r="N91" s="5">
         <v>20.71984013538918</v>
@@ -4800,7 +4800,7 @@
         <v>2084.62</v>
       </c>
       <c r="C92" s="4">
-        <v>2248.09</v>
+        <v>1931.25</v>
       </c>
       <c r="D92" s="4">
         <v>1797.65</v>
@@ -4809,7 +4809,7 @@
         <v>15292.14</v>
       </c>
       <c r="F92" s="4">
-        <v>17317.81</v>
+        <v>14877.01</v>
       </c>
       <c r="G92" s="4">
         <v>12699.92</v>
@@ -4821,7 +4821,7 @@
         <v>32370.13</v>
       </c>
       <c r="J92" s="4">
-        <v>35055.18</v>
+        <v>30114.38</v>
       </c>
       <c r="K92" s="4">
         <v>33113.24</v>
@@ -4830,7 +4830,7 @@
         <v>117020.9</v>
       </c>
       <c r="M92" s="4">
-        <v>116201.79</v>
+        <v>98747.28999999999</v>
       </c>
       <c r="N92" s="4">
         <v>83581.92999999999</v>
@@ -4850,7 +4850,7 @@
         <v>432.54</v>
       </c>
       <c r="E93" s="4">
-        <v>2821.746077777777</v>
+        <v>2821.746077777778</v>
       </c>
       <c r="F93" s="4">
         <v>2499.65</v>
@@ -4862,7 +4862,7 @@
         <v>3009.84</v>
       </c>
       <c r="I93" s="4">
-        <v>3973.133400000002</v>
+        <v>3973.1334</v>
       </c>
       <c r="J93" s="4">
         <v>4143.75</v>
@@ -4888,7 +4888,7 @@
         <v>17.80463159286158</v>
       </c>
       <c r="C94" s="5">
-        <v>17.99527598984027</v>
+        <v>20.94757281553398</v>
       </c>
       <c r="D94" s="5">
         <v>24.06141351208522</v>
@@ -4897,7 +4897,7 @@
         <v>18.45226422055891</v>
       </c>
       <c r="F94" s="5">
-        <v>14.43398443567633</v>
+        <v>16.80209934657569</v>
       </c>
       <c r="G94" s="5">
         <v>23.6996768483581</v>
@@ -4909,7 +4909,7 @@
         <v>12.2740730420298</v>
       </c>
       <c r="J94" s="5">
-        <v>11.82064961583424</v>
+        <v>13.76003756344975</v>
       </c>
       <c r="K94" s="5">
         <v>13.82703716096643</v>
@@ -4918,7 +4918,7 @@
         <v>12.29720916425091</v>
       </c>
       <c r="M94" s="5">
-        <v>17.76706709939666</v>
+        <v>20.90756110876562</v>
       </c>
       <c r="N94" s="5">
         <v>19.98112510682632</v>
@@ -5460,7 +5460,7 @@
         <v>0</v>
       </c>
       <c r="C107" s="4">
-        <v>85280.56</v>
+        <v>22626.14</v>
       </c>
       <c r="D107" s="4">
         <v>39606.79</v>
@@ -5469,7 +5469,7 @@
         <v>360.39</v>
       </c>
       <c r="F107" s="4">
-        <v>375076.89</v>
+        <v>100758.63</v>
       </c>
       <c r="G107" s="4">
         <v>292245.28</v>
@@ -5481,7 +5481,7 @@
         <v>360.39</v>
       </c>
       <c r="J107" s="4">
-        <v>804763.6899999999</v>
+        <v>214263.57</v>
       </c>
       <c r="K107" s="4">
         <v>597657.1</v>
@@ -5490,7 +5490,7 @@
         <v>981.17</v>
       </c>
       <c r="M107" s="4">
-        <v>2296585.21</v>
+        <v>630890.0699999999</v>
       </c>
       <c r="N107" s="4">
         <v>1840636.65</v>
@@ -5510,7 +5510,7 @@
         <v>1735.7</v>
       </c>
       <c r="E108" s="4">
-        <v>8133.588555555554</v>
+        <v>8133.588555555556</v>
       </c>
       <c r="F108" s="4">
         <v>11965.22</v>
@@ -5531,7 +5531,7 @@
         <v>22937.36</v>
       </c>
       <c r="L108" s="4">
-        <v>88868.51037499998</v>
+        <v>88868.510375</v>
       </c>
       <c r="M108" s="4">
         <v>112908.12</v>
@@ -5548,16 +5548,16 @@
         <v>0</v>
       </c>
       <c r="C109" s="5">
-        <v>2.174094541593067</v>
+        <v>8.194415839378701</v>
       </c>
       <c r="D109" s="5">
         <v>4.382329393520656</v>
       </c>
       <c r="E109" s="5">
-        <v>2256.885195359348</v>
+        <v>2256.885195359349</v>
       </c>
       <c r="F109" s="5">
-        <v>3.190071241126052</v>
+        <v>11.87513168847175</v>
       </c>
       <c r="G109" s="5">
         <v>5.040752069631373</v>
@@ -5569,16 +5569,16 @@
         <v>3659.484385742607</v>
       </c>
       <c r="J109" s="5">
-        <v>2.370111902041704</v>
+        <v>8.902026602095727</v>
       </c>
       <c r="K109" s="5">
         <v>3.837879613577753</v>
       </c>
       <c r="L109" s="5">
-        <v>9057.401915570184</v>
+        <v>9057.401915570186</v>
       </c>
       <c r="M109" s="5">
-        <v>4.916347954709679</v>
+        <v>17.89663926712304</v>
       </c>
       <c r="N109" s="5">
         <v>6.92577755636888</v>
@@ -5642,7 +5642,7 @@
         <v>742.2</v>
       </c>
       <c r="E111" s="4">
-        <v>3440.517777777778</v>
+        <v>3440.517777777777</v>
       </c>
       <c r="F111" s="4">
         <v>4008.69</v>
@@ -6323,7 +6323,7 @@
         <v>1788.62</v>
       </c>
       <c r="L126" s="4">
-        <v>10803.37867222222</v>
+        <v>10803.37867222223</v>
       </c>
       <c r="M126" s="4">
         <v>13603.7</v>
@@ -6434,7 +6434,7 @@
         <v>425.13</v>
       </c>
       <c r="E129" s="4">
-        <v>7825.644633333335</v>
+        <v>7825.644633333334</v>
       </c>
       <c r="F129" s="4">
         <v>7950.03</v>
@@ -6455,7 +6455,7 @@
         <v>7975.26</v>
       </c>
       <c r="L129" s="4">
-        <v>76227.76731111111</v>
+        <v>76227.76731111114</v>
       </c>
       <c r="M129" s="4">
         <v>74264.48</v>
@@ -6578,7 +6578,7 @@
         <v>15855.89</v>
       </c>
       <c r="I132" s="4">
-        <v>22456.05278333333</v>
+        <v>22456.05278333335</v>
       </c>
       <c r="J132" s="4">
         <v>24178.1</v>
@@ -6587,7 +6587,7 @@
         <v>26370.3</v>
       </c>
       <c r="L132" s="4">
-        <v>86140.16428888892</v>
+        <v>86140.1642888889</v>
       </c>
       <c r="M132" s="4">
         <v>99366.89999999999</v>
@@ -6830,7 +6830,7 @@
         <v>1327.06</v>
       </c>
       <c r="E138" s="4">
-        <v>7732.195972222221</v>
+        <v>7732.195972222218</v>
       </c>
       <c r="F138" s="4">
         <v>6945.5</v>
@@ -6842,7 +6842,7 @@
         <v>8301.610000000001</v>
       </c>
       <c r="I138" s="4">
-        <v>14496.8998611111</v>
+        <v>14496.89986111111</v>
       </c>
       <c r="J138" s="4">
         <v>14041.75</v>
@@ -6851,7 +6851,7 @@
         <v>17130.18</v>
       </c>
       <c r="L138" s="4">
-        <v>48944.2826388889</v>
+        <v>48944.28263888886</v>
       </c>
       <c r="M138" s="4">
         <v>60162.25</v>
@@ -6886,7 +6886,7 @@
         <v>372.8513554785046</v>
       </c>
       <c r="I139" s="5">
-        <v>9060.562413194439</v>
+        <v>9060.562413194446</v>
       </c>
       <c r="J139" s="5">
         <v>147.8689101187016</v>
@@ -6895,7 +6895,7 @@
         <v>415.4745042492918</v>
       </c>
       <c r="L139" s="5">
-        <v>14395.37724673203</v>
+        <v>14395.37724673202</v>
       </c>
       <c r="M139" s="5">
         <v>125.7147460222467</v>
@@ -7502,7 +7502,7 @@
         <v>4308.91</v>
       </c>
       <c r="I153" s="4">
-        <v>8264.485672222223</v>
+        <v>8264.485672222221</v>
       </c>
       <c r="J153" s="4">
         <v>8033.68</v>
@@ -7745,7 +7745,7 @@
         <v>169</v>
       </c>
       <c r="B159" s="4">
-        <v>279.93625</v>
+        <v>421.4577777777778</v>
       </c>
       <c r="C159" s="4">
         <v>823.71</v>
@@ -7754,7 +7754,7 @@
         <v>640.54</v>
       </c>
       <c r="E159" s="4">
-        <v>3748.308194444445</v>
+        <v>3889.829722222223</v>
       </c>
       <c r="F159" s="4">
         <v>5645.97</v>
@@ -7766,7 +7766,7 @@
         <v>4527.49</v>
       </c>
       <c r="I159" s="4">
-        <v>6062.135416666667</v>
+        <v>6203.656944444444</v>
       </c>
       <c r="J159" s="4">
         <v>8526.41</v>
@@ -7775,7 +7775,7 @@
         <v>7329</v>
       </c>
       <c r="L159" s="4">
-        <v>39142.51402777778</v>
+        <v>39284.03555555557</v>
       </c>
       <c r="M159" s="4">
         <v>58107.12</v>
@@ -8496,7 +8496,7 @@
         <v>108186.91</v>
       </c>
       <c r="C178" s="4">
-        <v>312753.22</v>
+        <v>236044.28</v>
       </c>
       <c r="D178" s="4">
         <v>166641.83</v>
@@ -8505,7 +8505,7 @@
         <v>1133005.32</v>
       </c>
       <c r="F178" s="4">
-        <v>2424435.539999999</v>
+        <v>1999181.94</v>
       </c>
       <c r="G178" s="4">
         <v>1351697.96</v>
@@ -8517,7 +8517,7 @@
         <v>2449098.87</v>
       </c>
       <c r="J178" s="4">
-        <v>4914058.540000002</v>
+        <v>4123315.76</v>
       </c>
       <c r="K178" s="4">
         <v>2875171.02</v>
@@ -8526,7 +8526,7 @@
         <v>6537634.020000001</v>
       </c>
       <c r="M178" s="4">
-        <v>15143733.21</v>
+        <v>12974270.55</v>
       </c>
       <c r="N178" s="4">
         <v>8941314.719999999</v>
@@ -8537,7 +8537,7 @@
         <v>187</v>
       </c>
       <c r="B179" s="4">
-        <v>45966.93779722222</v>
+        <v>46108.459325</v>
       </c>
       <c r="C179" s="4">
         <v>47156.68000000001</v>
@@ -8546,7 +8546,7 @@
         <v>49396.63</v>
       </c>
       <c r="E179" s="4">
-        <v>334299.2570277777</v>
+        <v>334440.7785555555</v>
       </c>
       <c r="F179" s="4">
         <v>346487.9799999998</v>
@@ -8558,7 +8558,7 @@
         <v>366174.4500000001</v>
       </c>
       <c r="I179" s="4">
-        <v>547520.4801305556</v>
+        <v>547662.0016583333</v>
       </c>
       <c r="J179" s="4">
         <v>595022.5500000003</v>
@@ -8567,7 +8567,7 @@
         <v>619358.6000000001</v>
       </c>
       <c r="L179" s="4">
-        <v>2690507.056736109</v>
+        <v>2690648.578263887</v>
       </c>
       <c r="M179" s="4">
         <v>2941870.97</v>
@@ -8581,19 +8581,19 @@
         <v>188</v>
       </c>
       <c r="B180" s="5">
-        <v>42.48844688994465</v>
+        <v>42.61925895193789</v>
       </c>
       <c r="C180" s="5">
-        <v>15.07791990119239</v>
+        <v>19.97789567279496</v>
       </c>
       <c r="D180" s="5">
         <v>29.64239530974905</v>
       </c>
       <c r="E180" s="5">
-        <v>29.50553286261514</v>
+        <v>29.51802367137655</v>
       </c>
       <c r="F180" s="5">
-        <v>14.29149071127706</v>
+        <v>17.33148809857695</v>
       </c>
       <c r="G180" s="5">
         <v>27.08996098507097</v>
@@ -8602,19 +8602,19 @@
         <v>27.08996098507097</v>
       </c>
       <c r="I180" s="5">
-        <v>22.35599741755447</v>
+        <v>22.36177593182808</v>
       </c>
       <c r="J180" s="5">
-        <v>12.10857675293384</v>
+        <v>14.43068114676719</v>
       </c>
       <c r="K180" s="5">
         <v>21.54162641775654</v>
       </c>
       <c r="L180" s="5">
-        <v>41.15413999170465</v>
+        <v>41.15630471257072</v>
       </c>
       <c r="M180" s="5">
-        <v>19.42632592112338</v>
+        <v>22.67465410608383</v>
       </c>
       <c r="N180" s="5">
         <v>32.71227992296865</v>
@@ -8625,19 +8625,19 @@
         <v>189</v>
       </c>
       <c r="B181" s="4">
-        <v>62219.9722027778</v>
+        <v>62078.45067500002</v>
       </c>
       <c r="C181" s="4">
-        <v>265596.54</v>
+        <v>188887.6</v>
       </c>
       <c r="D181" s="4">
         <v>117245.2</v>
       </c>
       <c r="E181" s="4">
-        <v>798706.0629722219</v>
+        <v>798564.5414444441</v>
       </c>
       <c r="F181" s="4">
-        <v>2077947.559999999</v>
+        <v>1652693.96</v>
       </c>
       <c r="G181" s="4">
         <v>985523.5099999998</v>
@@ -8646,19 +8646,19 @@
         <v>985523.5099999998</v>
       </c>
       <c r="I181" s="4">
-        <v>1901578.389869444</v>
+        <v>1901436.868341666</v>
       </c>
       <c r="J181" s="4">
-        <v>4319035.990000002</v>
+        <v>3528293.21</v>
       </c>
       <c r="K181" s="4">
         <v>2255812.42</v>
       </c>
       <c r="L181" s="4">
-        <v>3847126.963263893</v>
+        <v>3846985.441736115</v>
       </c>
       <c r="M181" s="4">
-        <v>12201862.24</v>
+        <v>10032399.58</v>
       </c>
       <c r="N181" s="4">
         <v>6016406.819999998</v>
